--- a/Ishikawa/Ishikawa-modelo.xlsx
+++ b/Ishikawa/Ishikawa-modelo.xlsx
@@ -498,7 +498,7 @@
     <t xml:space="preserve">Confirmada</t>
   </si>
   <si>
-    <t xml:space="preserve">Rotas cruzadas em 31 das 50 saídas</t>
+    <t xml:space="preserve">Em 31 das 50 saídas, outro entregador saiu para o mesmo bairro menos de 10 minutos depois</t>
   </si>
   <si>
     <t xml:space="preserve">Sim</t>
@@ -909,7 +909,7 @@
     <t xml:space="preserve">Comparar entregadores disponíveis e pedidos por hora</t>
   </si>
   <si>
-    <t xml:space="preserve">Pizza pronta esperou entregador em 46% dos atrasos</t>
+    <t xml:space="preserve">Mesmo número de entregadores todos os dias; nas sextas e nos sábados, 74 entregas por noite, contra 35 nos outros dias</t>
   </si>
   <si>
     <t xml:space="preserve">Expedição sem responsável definido no pico</t>
@@ -933,7 +933,7 @@
     <t xml:space="preserve">Medir o tempo de espera antes do forno</t>
   </si>
   <si>
-    <t xml:space="preserve">Fila no forno em 27% dos atrasos. Fica para o próximo ciclo</t>
+    <t xml:space="preserve">Espera média de 12 minutos antes do forno no pico, contra 3 fora dele. Fica para o próximo ciclo</t>
   </si>
   <si>
     <t xml:space="preserve">Motos com manutenção atrasada</t>
@@ -969,7 +969,7 @@
     <t xml:space="preserve">Há bolsas para todos os entregadores</t>
   </si>
   <si>
-    <t xml:space="preserve">Tempo de entrega medido só pela média do dia</t>
+    <t xml:space="preserve">Tempo de entrega medido só pela média do dia (causa de não detecção)</t>
   </si>
   <si>
     <t xml:space="preserve">O relatório padrão do aplicativo não separa por horário</t>
@@ -978,7 +978,7 @@
     <t xml:space="preserve">Refazer o indicador por faixa de horário</t>
   </si>
   <si>
-    <t xml:space="preserve">No prazo: 96% fora do pico e 68% no pico</t>
+    <t xml:space="preserve">No prazo: 91% fora do pico e 68% no pico. A média do dia, de 82%, escondia o pico</t>
   </si>
   <si>
     <t xml:space="preserve">Prazo prometido igual para todos os bairros</t>
@@ -1031,7 +1031,7 @@
     <t xml:space="preserve">Gerente de Suprimentos</t>
   </si>
   <si>
-    <t xml:space="preserve">Suprimentos</t>
+    <t xml:space="preserve">Distribuidora de materiais elétricos · Compras</t>
   </si>
   <si>
     <t xml:space="preserve">Equipe de compras</t>
@@ -4687,12 +4687,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H6:H17" type="date">
+      <formula1>36526</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I6:I17" type="list">
       <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H6:H17" type="date">
-      <formula1>36526</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/Ishikawa/Ishikawa-modelo.xlsx
+++ b/Ishikawa/Ishikawa-modelo.xlsx
@@ -906,7 +906,7 @@
     <t xml:space="preserve">Não</t>
   </si>
   <si>
-    <t xml:space="preserve">Comparar entregadores disponíveis e pedidos por hora</t>
+    <t xml:space="preserve">Comparar os entregadores disponíveis e as entregas por noite</t>
   </si>
   <si>
     <t xml:space="preserve">Mesmo número de entregadores todos os dias; nas sextas e nos sábados, 74 entregas por noite, contra 35 nos outros dias</t>
@@ -4687,12 +4687,12 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
+    <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I6:I17" type="list">
+      <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Digite uma data no formato dia/mês/ano." errorStyle="stop" errorTitle="Data inválida" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H6:H17" type="date">
       <formula1>36526</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Escolha uma das opções da lista." errorStyle="stop" errorTitle="Valor inválido" operator="between" prompt="Não iniciada, Em andamento, Concluída ou Cancelada" promptTitle="Opções" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I6:I17" type="list">
-      <formula1>"Não iniciada,Em andamento,Concluída,Cancelada"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
